--- a/tests/fixtures/rich/rich-text-github-sample01.xlsx
+++ b/tests/fixtures/rich/rich-text-github-sample01.xlsx
@@ -3,11 +3,6 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/igapyon/Documents/git/xlsx2md/tests/fixtures/rich/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF71EB6-E59F-9249-8002-71D6FF5495F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="600" windowWidth="27340" windowHeight="16760" xr2:uid="{95EFFC77-0BB9-C24C-8C40-5FB8F9D33BDC}"/>

--- a/tests/fixtures/rich/rich-text-github-sample01.xlsx
+++ b/tests/fixtures/rich/rich-text-github-sample01.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EF71EB6-E59F-9249-8002-71D6FF5495F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{71328DC5-6074-9347-9537-ECB4C03E5807}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1240" yWindow="600" windowWidth="27340" windowHeight="16760" xr2:uid="{95EFFC77-0BB9-C24C-8C40-5FB8F9D33BDC}"/>
   </bookViews>
@@ -156,44 +156,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">重要, </t>
-    </r>
-    <r>
-      <rPr>
-        <u/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Meiryo UI"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>取消線</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Meiryo UI"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="16"/>
-        <color theme="1"/>
-        <rFont val="Meiryo UI"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t>強調</t>
-    </r>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <r>
       <t>italic</t>
     </r>
     <r>
@@ -249,6 +211,71 @@
   </si>
   <si>
     <t>italic+strike</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">重要, </t>
+    </r>
+    <r>
+      <rPr>
+        <u/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>下線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <strike/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>取消線</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>,</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Meiryo UI"/>
+        <family val="2"/>
+        <charset val="128"/>
+      </rPr>
+      <t>強調</t>
+    </r>
+    <rPh sb="4" eb="6">
+      <t xml:space="preserve">カセン </t>
+    </rPh>
+    <rPh sb="7" eb="8">
+      <t xml:space="preserve">トリケシセン </t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -853,10 +880,10 @@
     </row>
     <row r="9" spans="1:3">
       <c r="A9" s="3" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B9" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="10" spans="1:3">
@@ -872,7 +899,7 @@
     </row>
     <row r="11" spans="1:3" ht="38">
       <c r="A11" s="12" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B11" s="7">
         <v>123</v>
@@ -883,7 +910,7 @@
     </row>
     <row r="12" spans="1:3">
       <c r="A12" s="2" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B12" s="10" t="s">
         <v>12</v>
